--- a/results/ranks_results.xlsx
+++ b/results/ranks_results.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\GDOforecast\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9AD01A27-F896-4F8F-A7AA-C14F60201555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE15AB1-188A-4E54-A6E3-8FE2850AB306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1032" windowWidth="20592" windowHeight="11928" xr2:uid="{B07C1D78-A0A5-4505-84DD-E19CC9DB1EE1}"/>
+    <workbookView xWindow="1960" yWindow="780" windowWidth="15190" windowHeight="11220" xr2:uid="{B07C1D78-A0A5-4505-84DD-E19CC9DB1EE1}"/>
   </bookViews>
   <sheets>
     <sheet name="75" sheetId="1" r:id="rId1"/>
     <sheet name="125" sheetId="2" r:id="rId2"/>
     <sheet name="175" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -940,12 +953,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F78250-4644-45F7-B703-05C4C02C79B2}">
   <dimension ref="A1:AH32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1010,7 +1023,7 @@
         <v>13</v>
       </c>
       <c r="Z1" t="str">
-        <f t="shared" ref="Z1:AI12" si="0">O1</f>
+        <f t="shared" ref="Z1:AH2" si="0">O1</f>
         <v>MAE</v>
       </c>
       <c r="AA1" t="str">
@@ -1046,7 +1059,7 @@
         <v>BIAS</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1147,7 +1160,7 @@
         <v>YW_AR_175</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1196,8 +1209,8 @@
         <v>2.6730769200000002</v>
       </c>
       <c r="Q3">
-        <f>INDEX(F$23:F$32,MATCH($N3,E$23:E$32,0))</f>
-        <v>6</v>
+        <f>INDEX(F$23:F$32,MATCH($N3,E$23:E$32,0))/75</f>
+        <v>0.08</v>
       </c>
       <c r="R3">
         <f>INDEX(H$23:H$32,MATCH($N3,G$23:G$32,0))</f>
@@ -1208,8 +1221,8 @@
         <v>2.5769230799999998</v>
       </c>
       <c r="T3">
-        <f>INDEX(L$23:L$32,MATCH($N3,K$23:K$32,0))</f>
-        <v>6.36538</v>
+        <f>INDEX(L$23:L$32,MATCH($N3,K$23:K$32,0))/125</f>
+        <v>5.0923040000000003E-2</v>
       </c>
       <c r="U3">
         <f>INDEX(N$23:N$32,MATCH($N3,M$23:M$32,0))</f>
@@ -1220,11 +1233,11 @@
         <v>3.8269230799999998</v>
       </c>
       <c r="W3">
-        <f>INDEX(R$23:R$32,MATCH($N3,Q$23:Q$32,0))</f>
-        <v>7.3653846200000004</v>
+        <f>INDEX(R$23:R$32,MATCH($N3,Q$23:Q$32,0))/175</f>
+        <v>4.2087912114285718E-2</v>
       </c>
       <c r="Y3" t="str">
-        <f t="shared" ref="Y2:Y12" si="1">N3</f>
+        <f t="shared" ref="Y3:Y12" si="1">N3</f>
         <v>fcast_avg</v>
       </c>
       <c r="Z3">
@@ -1237,7 +1250,7 @@
       </c>
       <c r="AB3">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0.08</v>
       </c>
       <c r="AC3">
         <f t="shared" si="2"/>
@@ -1249,7 +1262,7 @@
       </c>
       <c r="AE3">
         <f t="shared" si="2"/>
-        <v>6.37</v>
+        <v>0.05</v>
       </c>
       <c r="AF3">
         <f t="shared" si="2"/>
@@ -1261,10 +1274,10 @@
       </c>
       <c r="AH3">
         <f t="shared" si="2"/>
-        <v>7.37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1313,8 +1326,8 @@
         <v>3.0384615400000001</v>
       </c>
       <c r="Q4">
-        <f t="shared" ref="Q4:Q12" si="5">INDEX(F$23:F$32,MATCH($N4,E$23:E$32,0))</f>
-        <v>4.4230769199999997</v>
+        <f t="shared" ref="Q4:Q12" si="5">INDEX(F$23:F$32,MATCH($N4,E$23:E$32,0))/75</f>
+        <v>5.8974358933333332E-2</v>
       </c>
       <c r="R4">
         <f t="shared" ref="R4:R12" si="6">INDEX(H$23:H$32,MATCH($N4,G$23:G$32,0))</f>
@@ -1325,8 +1338,8 @@
         <v>3.1923076899999998</v>
       </c>
       <c r="T4">
-        <f t="shared" ref="T4:T12" si="8">INDEX(L$23:L$32,MATCH($N4,K$23:K$32,0))</f>
-        <v>4.5192307700000001</v>
+        <f t="shared" ref="T4:T12" si="8">INDEX(L$23:L$32,MATCH($N4,K$23:K$32,0))/125</f>
+        <v>3.6153846160000003E-2</v>
       </c>
       <c r="U4">
         <f t="shared" ref="U4:U12" si="9">INDEX(N$23:N$32,MATCH($N4,M$23:M$32,0))</f>
@@ -1337,8 +1350,8 @@
         <v>2.5</v>
       </c>
       <c r="W4">
-        <f t="shared" ref="W4:W12" si="11">INDEX(R$23:R$32,MATCH($N4,Q$23:Q$32,0))</f>
-        <v>5.4807692299999999</v>
+        <f t="shared" ref="W4:W12" si="11">INDEX(R$23:R$32,MATCH($N4,Q$23:Q$32,0))/175</f>
+        <v>3.1318681314285716E-2</v>
       </c>
       <c r="Y4" t="str">
         <f t="shared" si="1"/>
@@ -1354,7 +1367,7 @@
       </c>
       <c r="AB4">
         <f t="shared" si="2"/>
-        <v>4.42</v>
+        <v>0.06</v>
       </c>
       <c r="AC4">
         <f t="shared" si="2"/>
@@ -1366,7 +1379,7 @@
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>4.5199999999999996</v>
+        <v>0.04</v>
       </c>
       <c r="AF4">
         <f t="shared" si="2"/>
@@ -1378,10 +1391,10 @@
       </c>
       <c r="AH4">
         <f t="shared" si="2"/>
-        <v>5.48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1431,7 +1444,7 @@
       </c>
       <c r="Q5">
         <f t="shared" si="5"/>
-        <v>5.6730769199999997</v>
+        <v>7.5641025599999995E-2</v>
       </c>
       <c r="R5">
         <f t="shared" si="6"/>
@@ -1443,7 +1456,7 @@
       </c>
       <c r="T5">
         <f t="shared" si="8"/>
-        <v>5.5961538500000003</v>
+        <v>4.4769230800000004E-2</v>
       </c>
       <c r="U5">
         <f t="shared" si="9"/>
@@ -1455,7 +1468,7 @@
       </c>
       <c r="W5">
         <f t="shared" si="11"/>
-        <v>5.3653846200000004</v>
+        <v>3.0659340685714288E-2</v>
       </c>
       <c r="Y5" t="str">
         <f t="shared" si="1"/>
@@ -1471,7 +1484,7 @@
       </c>
       <c r="AB5">
         <f t="shared" si="2"/>
-        <v>5.67</v>
+        <v>0.08</v>
       </c>
       <c r="AC5">
         <f t="shared" si="2"/>
@@ -1483,7 +1496,7 @@
       </c>
       <c r="AE5">
         <f t="shared" si="2"/>
-        <v>5.6</v>
+        <v>0.04</v>
       </c>
       <c r="AF5">
         <f t="shared" si="2"/>
@@ -1495,10 +1508,10 @@
       </c>
       <c r="AH5">
         <f t="shared" si="2"/>
-        <v>5.37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1548,7 +1561,7 @@
       </c>
       <c r="Q6">
         <f t="shared" si="5"/>
-        <v>4.1153846200000004</v>
+        <v>5.4871794933333336E-2</v>
       </c>
       <c r="R6">
         <f t="shared" si="6"/>
@@ -1560,7 +1573,7 @@
       </c>
       <c r="T6">
         <f t="shared" si="8"/>
-        <v>4.0961538500000003</v>
+        <v>3.27692308E-2</v>
       </c>
       <c r="U6">
         <f t="shared" si="9"/>
@@ -1572,7 +1585,7 @@
       </c>
       <c r="W6">
         <f t="shared" si="11"/>
-        <v>4.0769230800000003</v>
+        <v>2.3296703314285717E-2</v>
       </c>
       <c r="Y6" t="str">
         <f t="shared" si="1"/>
@@ -1588,7 +1601,7 @@
       </c>
       <c r="AB6">
         <f t="shared" si="2"/>
-        <v>4.12</v>
+        <v>0.05</v>
       </c>
       <c r="AC6">
         <f t="shared" si="2"/>
@@ -1600,7 +1613,7 @@
       </c>
       <c r="AE6">
         <f t="shared" si="2"/>
-        <v>4.0999999999999996</v>
+        <v>0.03</v>
       </c>
       <c r="AF6">
         <f t="shared" si="2"/>
@@ -1612,10 +1625,10 @@
       </c>
       <c r="AH6">
         <f t="shared" si="2"/>
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -1665,7 +1678,7 @@
       </c>
       <c r="Q7">
         <f t="shared" si="5"/>
-        <v>5.8653846200000004</v>
+        <v>7.8205128266666674E-2</v>
       </c>
       <c r="R7">
         <f t="shared" si="6"/>
@@ -1677,7 +1690,7 @@
       </c>
       <c r="T7">
         <f t="shared" si="8"/>
-        <v>5.6730769199999997</v>
+        <v>4.5384615359999998E-2</v>
       </c>
       <c r="U7">
         <f t="shared" si="9"/>
@@ -1689,7 +1702,7 @@
       </c>
       <c r="W7">
         <f t="shared" si="11"/>
-        <v>5.4807692299999999</v>
+        <v>3.1318681314285716E-2</v>
       </c>
       <c r="Y7" t="str">
         <f t="shared" si="1"/>
@@ -1705,7 +1718,7 @@
       </c>
       <c r="AB7">
         <f t="shared" si="2"/>
-        <v>5.87</v>
+        <v>0.08</v>
       </c>
       <c r="AC7">
         <f t="shared" si="2"/>
@@ -1717,7 +1730,7 @@
       </c>
       <c r="AE7">
         <f t="shared" si="2"/>
-        <v>5.67</v>
+        <v>0.05</v>
       </c>
       <c r="AF7">
         <f t="shared" si="2"/>
@@ -1729,10 +1742,10 @@
       </c>
       <c r="AH7">
         <f t="shared" si="2"/>
-        <v>5.48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -1782,7 +1795,7 @@
       </c>
       <c r="Q8">
         <f t="shared" si="5"/>
-        <v>4.5576923100000002</v>
+        <v>6.0769230800000004E-2</v>
       </c>
       <c r="R8">
         <f t="shared" si="6"/>
@@ -1794,7 +1807,7 @@
       </c>
       <c r="T8">
         <f t="shared" si="8"/>
-        <v>4.3846153799999996</v>
+        <v>3.5076923039999999E-2</v>
       </c>
       <c r="U8">
         <f t="shared" si="9"/>
@@ -1806,7 +1819,7 @@
       </c>
       <c r="W8">
         <f t="shared" si="11"/>
-        <v>4.3461538500000003</v>
+        <v>2.483516485714286E-2</v>
       </c>
       <c r="Y8" t="str">
         <f t="shared" si="1"/>
@@ -1822,7 +1835,7 @@
       </c>
       <c r="AB8">
         <f t="shared" si="2"/>
-        <v>4.5599999999999996</v>
+        <v>0.06</v>
       </c>
       <c r="AC8">
         <f t="shared" si="2"/>
@@ -1834,7 +1847,7 @@
       </c>
       <c r="AE8">
         <f t="shared" si="2"/>
-        <v>4.38</v>
+        <v>0.04</v>
       </c>
       <c r="AF8">
         <f t="shared" si="2"/>
@@ -1846,10 +1859,10 @@
       </c>
       <c r="AH8">
         <f t="shared" si="2"/>
-        <v>4.3499999999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1899,7 +1912,7 @@
       </c>
       <c r="Q9">
         <f t="shared" si="5"/>
-        <v>3.1346153800000001</v>
+        <v>4.1794871733333336E-2</v>
       </c>
       <c r="R9">
         <f t="shared" si="6"/>
@@ -1911,7 +1924,7 @@
       </c>
       <c r="T9">
         <f t="shared" si="8"/>
-        <v>2.8846153800000001</v>
+        <v>2.3076923039999999E-2</v>
       </c>
       <c r="U9">
         <f t="shared" si="9"/>
@@ -1923,7 +1936,7 @@
       </c>
       <c r="W9">
         <f t="shared" si="11"/>
-        <v>2.8076923100000002</v>
+        <v>1.6043956057142858E-2</v>
       </c>
       <c r="Y9" t="str">
         <f t="shared" si="1"/>
@@ -1939,7 +1952,7 @@
       </c>
       <c r="AB9">
         <f t="shared" si="2"/>
-        <v>3.13</v>
+        <v>0.04</v>
       </c>
       <c r="AC9">
         <f t="shared" si="2"/>
@@ -1951,7 +1964,7 @@
       </c>
       <c r="AE9">
         <f t="shared" si="2"/>
-        <v>2.88</v>
+        <v>0.02</v>
       </c>
       <c r="AF9">
         <f t="shared" si="2"/>
@@ -1963,10 +1976,10 @@
       </c>
       <c r="AH9">
         <f t="shared" si="2"/>
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2016,7 +2029,7 @@
       </c>
       <c r="Q10">
         <f t="shared" si="5"/>
-        <v>4.0576923100000002</v>
+        <v>5.4102564133333336E-2</v>
       </c>
       <c r="R10">
         <f t="shared" si="6"/>
@@ -2028,7 +2041,7 @@
       </c>
       <c r="T10">
         <f t="shared" si="8"/>
-        <v>4.2115384599999999</v>
+        <v>3.3692307679999998E-2</v>
       </c>
       <c r="U10">
         <f t="shared" si="9"/>
@@ -2040,7 +2053,7 @@
       </c>
       <c r="W10">
         <f t="shared" si="11"/>
-        <v>3.5769230799999998</v>
+        <v>2.0439560457142857E-2</v>
       </c>
       <c r="Y10" t="str">
         <f t="shared" si="1"/>
@@ -2056,7 +2069,7 @@
       </c>
       <c r="AB10">
         <f t="shared" si="2"/>
-        <v>4.0599999999999996</v>
+        <v>0.05</v>
       </c>
       <c r="AC10">
         <f t="shared" si="2"/>
@@ -2068,7 +2081,7 @@
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>4.21</v>
+        <v>0.03</v>
       </c>
       <c r="AF10">
         <f t="shared" si="2"/>
@@ -2080,10 +2093,10 @@
       </c>
       <c r="AH10">
         <f t="shared" si="2"/>
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2133,7 +2146,7 @@
       </c>
       <c r="Q11">
         <f t="shared" si="5"/>
-        <v>8.1153846200000004</v>
+        <v>0.10820512826666667</v>
       </c>
       <c r="R11">
         <f t="shared" si="6"/>
@@ -2145,7 +2158,7 @@
       </c>
       <c r="T11">
         <f t="shared" si="8"/>
-        <v>8.1153846200000004</v>
+        <v>6.4923076960000006E-2</v>
       </c>
       <c r="U11">
         <f t="shared" si="9"/>
@@ -2157,7 +2170,7 @@
       </c>
       <c r="W11">
         <f t="shared" si="11"/>
-        <v>7.75</v>
+        <v>4.4285714285714282E-2</v>
       </c>
       <c r="Y11" t="str">
         <f t="shared" si="1"/>
@@ -2173,7 +2186,7 @@
       </c>
       <c r="AB11">
         <f t="shared" si="2"/>
-        <v>8.1199999999999992</v>
+        <v>0.11</v>
       </c>
       <c r="AC11">
         <f t="shared" si="2"/>
@@ -2185,7 +2198,7 @@
       </c>
       <c r="AE11">
         <f t="shared" si="2"/>
-        <v>8.1199999999999992</v>
+        <v>0.06</v>
       </c>
       <c r="AF11">
         <f t="shared" si="2"/>
@@ -2197,10 +2210,10 @@
       </c>
       <c r="AH11">
         <f t="shared" si="2"/>
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -2250,7 +2263,7 @@
       </c>
       <c r="Q12">
         <f t="shared" si="5"/>
-        <v>9.0576923100000002</v>
+        <v>0.1207692308</v>
       </c>
       <c r="R12">
         <f t="shared" si="6"/>
@@ -2262,7 +2275,7 @@
       </c>
       <c r="T12">
         <f t="shared" si="8"/>
-        <v>9.1538500000000003</v>
+        <v>7.3230799999999999E-2</v>
       </c>
       <c r="U12">
         <f t="shared" si="9"/>
@@ -2274,7 +2287,7 @@
       </c>
       <c r="W12">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>0.05</v>
       </c>
       <c r="Y12" t="str">
         <f t="shared" si="1"/>
@@ -2290,7 +2303,7 @@
       </c>
       <c r="AB12">
         <f t="shared" si="2"/>
-        <v>9.06</v>
+        <v>0.12</v>
       </c>
       <c r="AC12">
         <f t="shared" si="2"/>
@@ -2302,7 +2315,7 @@
       </c>
       <c r="AE12">
         <f t="shared" si="2"/>
-        <v>9.15</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AF12">
         <f t="shared" si="2"/>
@@ -2314,10 +2327,10 @@
       </c>
       <c r="AH12">
         <f t="shared" si="2"/>
-        <v>8.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -2355,7 +2368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -2393,7 +2406,7 @@
         <v>6.7884615400000001</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -2431,7 +2444,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -2469,7 +2482,7 @@
         <v>6.7884615400000001</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2507,7 +2520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -2545,7 +2558,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -2601,7 +2614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -2657,7 +2670,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -2713,7 +2726,7 @@
         <v>2.8076923100000002</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -2769,7 +2782,7 @@
         <v>3.5769230799999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2825,7 +2838,7 @@
         <v>4.0769230800000003</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -2881,7 +2894,7 @@
         <v>4.3461538500000003</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -2937,7 +2950,7 @@
         <v>5.3653846200000004</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -2993,7 +3006,7 @@
         <v>5.4807692299999999</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -3049,7 +3062,7 @@
         <v>5.4807692299999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -3105,7 +3118,7 @@
         <v>7.3653846200000004</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -3161,7 +3174,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -3225,12 +3238,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E51DAA-1550-4E56-8025-EEA52A22953A}">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.44140625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3271,7 +3284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3312,7 +3325,7 @@
         <v>7.2884615400000001</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3353,7 +3366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3394,7 +3407,7 @@
         <v>7.2884615400000001</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3435,7 +3448,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -3484,12 +3497,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B5AB81-B724-49EA-9DDE-FD0BAB27FB92}">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3530,7 +3543,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3571,7 +3584,7 @@
         <v>6.7884615400000001</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3612,7 +3625,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3653,7 +3666,7 @@
         <v>6.7884615400000001</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3694,7 +3707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
